--- a/docs/test-cases/SPM-55_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-55_Test_Cases.xlsx
@@ -27,7 +27,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -51,6 +51,9 @@
       <color rgb="FF1155CC"/>
       <sz val="10"/>
       <u val="single"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
     </font>
   </fonts>
   <fills count="4">
@@ -136,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -183,6 +186,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -475,12 +481,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.75" customHeight="1" s="19">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="22" t="inlineStr">
         <is>
           <t>SPM-55: As Technical Support Staff, I want to record equipment as unavailable, damaged or under maintenance so that it is not considered available for event reservations</t>
         </is>
@@ -492,32 +498,32 @@
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="22" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="22" t="inlineStr">
         <is>
           <t>Linked AC</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" s="22" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -544,27 +550,27 @@
           <t>TC01</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>SPM-55-TC01</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>Technical Support record some units of an item as under maintenance, with a reason</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t>AC1, AC2, AC6</t>
         </is>
       </c>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -583,27 +589,27 @@
           <t>TC02</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>SPM-55-TC02</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>Units out of service are left out of the availability check and of what Reserve takes</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="E5" s="18" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -622,27 +628,27 @@
           <t>TC03</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>SPM-55-TC03</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>Returning every unit to available counts them in the availability check again</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>AC5, AC3</t>
         </is>
       </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -661,27 +667,27 @@
           <t>TC04</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>SPM-55-TC04</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>Every unit of an item can be marked damaged, without a reason</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>AC1, AC2</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -700,27 +706,27 @@
           <t>TC05</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>SPM-55-TC05</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>More units than the item has cannot be marked out of service</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E8" s="18" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -739,27 +745,27 @@
           <t>TC06</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>SPM-55-TC06</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>A reservation left short is flagged for review, not cancelled, and its Coordinator notified</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -778,27 +784,27 @@
           <t>TC07</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>SPM-55-TC07</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>A reservation that is exactly covered by the units left is not flagged</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -817,27 +823,27 @@
           <t>TC08</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>SPM-55-TC08</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>When two events on the same days can no longer both be covered, both are flagged</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -856,27 +862,27 @@
           <t>TC09</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>SPM-55-TC09</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>Technical Support can return some of an item's units and leave the rest out of service</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -895,38 +901,42 @@
           <t>TC10</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>SPM-55-TC10</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>A Coordinator and the Operations Manager can see each item's operational status but not change it</t>
         </is>
       </c>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>AC6</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
       <c r="G13" s="23" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="H13" s="23" t="n"/>
-      <c r="I13" s="23" t="n"/>
+      <c r="I13" s="23" t="inlineStr">
+        <is>
+          <t>Week 7 #5</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
@@ -934,27 +944,27 @@
           <t>TC11</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>SPM-55-TC11</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>The Event Organiser and Venue Staff cannot see equipment status</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>AC6, AC1</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -968,20 +978,21 @@
       <c r="I14" s="23" t="n"/>
     </row>
     <row r="15"/>
+    <row r="16"/>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" s="22" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>Acceptance Criterion</t>
         </is>
       </c>
       <c r="C17" s="20" t="n"/>
       <c r="D17" s="21" t="n"/>
-      <c r="E17" s="1" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>Covered by</t>
         </is>
@@ -989,19 +1000,19 @@
       <c r="F17" s="21" t="n"/>
     </row>
     <row r="18" ht="57.75" customHeight="1" s="19">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="23" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Technical Support Staff can mark a piece of equipment as unavailable, damaged, or under maintenance.</t>
         </is>
       </c>
       <c r="C18" s="20" t="n"/>
       <c r="D18" s="21" t="n"/>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>SPM-55-TC01
 SPM-55-TC04
@@ -1012,19 +1023,19 @@
       <c r="F18" s="21" t="n"/>
     </row>
     <row r="19" ht="30.75" customHeight="1" s="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="23" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>Technical Support Staff can provide a reason for the unavailability.</t>
         </is>
       </c>
       <c r="C19" s="20" t="n"/>
       <c r="D19" s="21" t="n"/>
-      <c r="E19" s="18" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>SPM-55-TC01
 SPM-55-TC04</t>
@@ -1033,19 +1044,19 @@
       <c r="F19" s="21" t="n"/>
     </row>
     <row r="20" ht="30.75" customHeight="1" s="19">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="23" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Equipment marked unavailable is excluded from the availability checks used in Check Equipment Availability and Reserve Equipment.</t>
         </is>
       </c>
       <c r="C20" s="20" t="n"/>
       <c r="D20" s="21" t="n"/>
-      <c r="E20" s="18" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>SPM-55-TC02
 SPM-55-TC03</t>
@@ -1054,19 +1065,19 @@
       <c r="F20" s="21" t="n"/>
     </row>
     <row r="21" ht="57.75" customHeight="1" s="19">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="23" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>Given marking equipment unavailable leaves an existing reservation for an upcoming event without sufficient quantity, when the status is recorded, then the reservation is flagged for review rather than cancelled, and the assigned Coordinator is notified.</t>
         </is>
       </c>
       <c r="C21" s="20" t="n"/>
       <c r="D21" s="21" t="n"/>
-      <c r="E21" s="18" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>SPM-55-TC06
 SPM-55-TC07
@@ -1076,19 +1087,19 @@
       <c r="F21" s="21" t="n"/>
     </row>
     <row r="22" ht="30.75" customHeight="1" s="19">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="23" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>Technical Support Staff can return equipment to an available status, after which it is counted in availability checks again.</t>
         </is>
       </c>
       <c r="C22" s="20" t="n"/>
       <c r="D22" s="21" t="n"/>
-      <c r="E22" s="18" t="inlineStr">
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>SPM-55-TC03
 SPM-55-TC09</t>
@@ -1097,19 +1108,19 @@
       <c r="F22" s="21" t="n"/>
     </row>
     <row r="23" ht="44.25" customHeight="1" s="19">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="23" t="inlineStr">
         <is>
           <t>AC6</t>
         </is>
       </c>
-      <c r="B23" s="18" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>Authorised users can view an equipment item's current operational status.</t>
         </is>
       </c>
       <c r="C23" s="20" t="n"/>
       <c r="D23" s="21" t="n"/>
-      <c r="E23" s="18" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>SPM-55-TC01
 SPM-55-TC10
@@ -1120,12 +1131,12 @@
     </row>
     <row r="24" ht="15.75" customHeight="1" s="19"/>
     <row r="25" ht="152.25" customHeight="1" s="19">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" s="22" t="inlineStr">
         <is>
           <t>Code reviewed</t>
         </is>
       </c>
-      <c r="B25" s="18" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>src/app/equipment/page.tsx
 src/app/api/equipment/[id]/out-of-service/route.ts
@@ -2185,7 +2196,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-55-TC08</t>
         </is>
@@ -2197,7 +2208,7 @@
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>When two events on the same days can no longer both be covered, both are flagged</t>
         </is>
@@ -2209,7 +2220,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>npm run fixtures:spm55 has been run. 'SPM55 Stage Monitor' has 6 units, none out of service. 3 are Reserved for 'SPM55 Morning Showcase' and 3 for 'SPM55 Evening Showcase', both on 17 Aug 2027. Logged in as Kenji Sato (kenji.sato@connectsphere.com / password123). This case changes the item - run npm run fixtures:spm55 afterwards.</t>
         </is>
@@ -2221,7 +2232,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>1. Click 'Equipment' in the sidebar
 2. Click 'Record unavailability' on the 'SPM55 Stage Monitor' row
@@ -2237,7 +2248,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Item: SPM55 Stage Monitor (6 units), 1 out of service
 Reservations: Morning Showcase 3 and Evening Showcase 3, same day</t>
@@ -2250,7 +2261,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Step 5: An amber panel reads 'Saved - 2 reservations flagged for review, coordinators notified' and lists both 'SPM55 Morning Showcase: 3 reserved' and 'SPM55 Evening Showcase: 3 reserved' - 5 units now have to cover 6, and the system does not choose which event loses out.</t>
         </is>
@@ -2262,7 +2273,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -2294,7 +2305,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>Step 5: An amber panel reads 'Saved - 2 reservations flagged for review, coordinators notified' and lists both 'SPM55 Morning Showcase: 3 reserved' and 'SPM55 Evening Showcase: 3 reserved' - 5 units now have to cover 6, and the system does not choose which event loses out.</t>
         </is>
@@ -2330,7 +2341,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -2361,7 +2372,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>Step 5: An amber panel reads 'Saved - 2 reservations flagged for review, coordinators notified' and lists both 'SPM55 Morning Showcase: 3 reserved' and 'SPM55 Evening Showcase: 3 reserved' - 5 units now have to cover 6, and the system does not choose which event loses out.</t>
         </is>
@@ -3424,7 +3435,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-55-TC09</t>
         </is>
@@ -3436,7 +3447,7 @@
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Technical Support can return some of an item's units and leave the rest out of service</t>
         </is>
@@ -3448,7 +3459,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>npm run fixtures:spm55 has been run. 'SPM55 Spare Microphone Kit' has 5 units, 3 of them out of service as 'Under maintenance - Cable fault'. Logged in as Kenji Sato (kenji.sato@connectsphere.com / password123). This case changes the item - run npm run fixtures:spm55 afterwards.</t>
         </is>
@@ -3460,7 +3471,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>1. Click 'Equipment' in the sidebar
 2. Click 'Record unavailability' on the 'SPM55 Spare Microphone Kit' row
@@ -3475,7 +3486,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Item: SPM55 Spare Microphone Kit (5 units), 3 out of service -&gt; 1</t>
         </is>
@@ -3487,7 +3498,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Step 2: The dialog opens filled in with 3, 'Under maintenance' and 'Cable fault'.
 Step 4: The message 'Saved. 1 of 5 SPM55 Spare Microphone Kit units are out of service. No reservations were affected.' is shown. The row shows Out of service 1, the status 'Partly out of service' and 'Under maintenance - Cable fault' - the 2 returned units are counted as available again.</t>
@@ -3500,7 +3511,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -3532,7 +3543,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>Step 2: The dialog opens filled in with 3, 'Under maintenance' and 'Cable fault'.
 Step 4: The message 'Saved. 1 of 5 SPM55 Spare Microphone Kit units are out of service. No reservations were affected.' is shown. The row shows Out of service 1, the status 'Partly out of service' and 'Under maintenance - Cable fault' - the 2 returned units are counted as available again.</t>
@@ -3569,7 +3580,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -3600,7 +3611,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>Step 2: The dialog opens filled in with 3, 'Under maintenance' and 'Cable fault'.
 Step 4: The message 'Saved. 1 of 5 SPM55 Spare Microphone Kit units are out of service. No reservations were affected.' is shown. The row shows Out of service 1, the status 'Partly out of service' and 'Under maintenance - Cable fault' - the 2 returned units are counted as available again.</t>
@@ -4642,7 +4653,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="19" min="1" max="1"/>
@@ -4650,57 +4661,64 @@
     <col width="12.63" customWidth="1" style="19" min="3" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="19">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="90" customHeight="1" s="19">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>v2 (2026-10-20): The Event Operations Manager is now shown as the 'Event Coordinator Lead' (SPM-84 AC1, forum #129, Week 7 Change #5) - the same role, accounts, permissions and pages. Read 'Operations Manager', 'Event Operations Manager' or 'Ops Manager' in this case as 'Event Coordinator Lead'; on screen the role is shown under its new name, and refusals say 'Assigning coordinators is the Event Coordinator Lead's role.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="19">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="4" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="19">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="18" t="inlineStr">
-        <is>
-          <t>SPM-55-TC10</t>
-        </is>
-      </c>
+      <c r="B2" s="4" t="n"/>
     </row>
     <row r="3" ht="30.75" customHeight="1" s="19">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="B3" s="18" t="inlineStr">
-        <is>
-          <t>A Coordinator and the Operations Manager can see each item's operational status but not change it</t>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>SPM-55-TC10</t>
         </is>
       </c>
     </row>
     <row r="4" ht="71.25" customHeight="1" s="19">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Pre-conditions</t>
-        </is>
-      </c>
-      <c r="B4" s="18" t="inlineStr">
-        <is>
-          <t>npm run fixtures:spm55 has been run ('SPM55 Spare Microphone Kit' has 3 of 5 units out of service as 'Under maintenance - Cable fault'; 'SPM55 Laser Projector' has none). Logged in as Event Coordinator Daniel Tan (daniel.tan@connectsphere.com / password123).</t>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>A Coordinator and the Operations Manager can see each item's operational status but not change it</t>
         </is>
       </c>
     </row>
     <row r="5" ht="84.75" customHeight="1" s="19">
       <c r="A5" s="6" t="inlineStr">
         <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>npm run fixtures:spm55 has been run ('SPM55 Spare Microphone Kit' has 3 of 5 units out of service as 'Under maintenance - Cable fault'; 'SPM55 Laser Projector' has none). Logged in as Event Coordinator Daniel Tan (daniel.tan@connectsphere.com / password123).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44.25" customHeight="1" s="19">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>1. Click 'Equipment' in the sidebar
 2. Click 'Log out' in the top bar
@@ -4709,192 +4727,191 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="44.25" customHeight="1" s="19">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="7" ht="98.25" customHeight="1" s="19">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Coordinator: daniel.tan@connectsphere.com
 Operations Manager: grace.lim@connectsphere.com (no Equipment link in the sidebar)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="98.25" customHeight="1" s="19">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="8" ht="17.25" customHeight="1" s="19">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Step 1: The Equipment page lists 'SPM55 Spare Microphone Kit' with Out of service 3, the status 'Partly out of service' and 'Under maintenance - Cable fault', and 'SPM55 Laser Projector' as 'Available'. There are no 'Record unavailability' or 'Return all to available' buttons.
 Step 4: Grace Lim sees the same list and statuses, also with no buttons.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="17.25" customHeight="1" s="19">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>Janelle</t>
-        </is>
-      </c>
-    </row>
     <row r="9" ht="15.75" customHeight="1" s="19">
       <c r="A9" s="6" t="inlineStr">
         <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1" s="19">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B10" s="16" t="n">
         <v>46306</v>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1" s="19"/>
-    <row r="11" ht="15.75" customHeight="1" s="19">
-      <c r="A11" s="11" t="inlineStr">
+    <row r="11" ht="15.75" customHeight="1" s="19"/>
+    <row r="12" ht="15.75" customHeight="1" s="19">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="13" t="n"/>
-    </row>
-    <row r="12" ht="15.75" customHeight="1" s="19">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="13" t="n"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" s="19">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>Step 1: The Equipment page lists 'SPM55 Spare Microphone Kit' with Out of service 3, the status 'Partly out of service' and 'Under maintenance - Cable fault', and 'SPM55 Laser Projector' as 'Available'. There are no 'Record unavailability' or 'Return all to available' buttons.
 Step 4: Grace Lim sees the same list and statuses, also with no buttons</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15.75" customHeight="1" s="19">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="14" ht="15.75" customHeight="1" s="19">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="19">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>Janelle</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" s="19">
       <c r="A16" s="15" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1" s="19">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B17" s="16" t="n">
         <v>46306</v>
       </c>
     </row>
-    <row r="17" ht="15.75" customHeight="1" s="19"/>
-    <row r="18" ht="15.75" customHeight="1" s="19">
-      <c r="A18" s="11" t="inlineStr">
+    <row r="18" ht="15.75" customHeight="1" s="19"/>
+    <row r="19" ht="15.75" customHeight="1" s="19">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1" s="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="B19" s="12" t="n"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" s="19">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Step 1: The Equipment page lists 'SPM55 Spare Microphone Kit' with Out of service 3, the status 'Partly out of service' and 'Under maintenance - Cable fault', and 'SPM55 Laser Projector' as 'Available'. There are no 'Record unavailability' or 'Return all to available' buttons.
 Step 4: Grace Lim sees the same list and statuses, also with no buttons</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15.75" customHeight="1" s="19">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="21" ht="15.75" customHeight="1" s="19">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="19">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>Executed by</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>Kristen</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="19">
       <c r="A23" s="15" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" s="19">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
+      <c r="B24" s="16" t="n">
         <v>46307</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1" s="19"/>
     <row r="25" ht="15.75" customHeight="1" s="19"/>
     <row r="26" ht="15.75" customHeight="1" s="19"/>
     <row r="27" ht="15.75" customHeight="1" s="19"/>
@@ -5872,6 +5889,9 @@
     <row r="999" ht="15.75" customHeight="1" s="19"/>
     <row r="1000" ht="15.75" customHeight="1" s="19"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -5905,7 +5925,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-55-TC11</t>
         </is>
@@ -5917,7 +5937,7 @@
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>The Event Organiser and Venue Staff cannot see equipment status</t>
         </is>
@@ -5929,7 +5949,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>npm run fixtures:spm55 has been run. Logged in as Event Organiser Rachel Ng (rachel.ng@meridianfina.com / password123).</t>
         </is>
@@ -5941,7 +5961,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>1. Type /equipment after the site address in the browser address bar (e.g. http://localhost:3000/equipment) and press Enter
 2. Click 'Log out' in the top bar
@@ -5956,7 +5976,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Organiser: rachel.ng@meridianfina.com
 Venue Staff: marcus.wong@connectsphere.com</t>
@@ -5969,7 +5989,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Step 1: The page shows 'You do not have access to this' and no equipment, status or reason is shown - equipment status is internal.
 Step 4: Marcus Wong sees the same refusal and no equipment.</t>
@@ -5982,7 +6002,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -6014,7 +6034,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>Step 1: The page shows 'You do not have access to this' and no equipment, status or reason is shown - equipment status is internal.
 Step 4: Marcus Wong sees the same refusal and no equipment.</t>
@@ -6051,7 +6071,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -6082,7 +6102,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>Step 1: The page shows 'You do not have access to this' and no equipment, status or reason is shown - equipment status is internal.
 Step 4: Marcus Wong sees the same refusal and no equipment.</t>
@@ -7134,76 +7154,76 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="22" t="inlineStr">
         <is>
           <t>Question / ambiguity for the PO or developer</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="22" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
     </row>
     <row r="2" ht="71.25" customHeight="1" s="19">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>DECIDED 2026-10-11: The screen is the sidebar 'Equipment' page (/equipment, currently 'not built yet'). Columns: Equipment, Category, Total units, Out of service, Status, Reason. Status badges: 'Available', 'Partly out of service', 'Out of service'. Reason column: '&lt;Type&gt; - &lt;reason&gt;', or the type alone.</t>
         </is>
       </c>
-      <c r="C2" s="18" t="n"/>
+      <c r="C2" s="23" t="n"/>
     </row>
     <row r="3" ht="138.75" customHeight="1" s="19">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>DECIDED 2026-10-11: Wording - button 'Record unavailability' opening a dialog 'Record unavailability - &lt;item&gt;' with 'Units out of service', 'Type' and 'Reason (optional)', and 'Save' / 'Cancel'; 'Return all to available' opening 'Return all units to available?' with 'Return to available'. Messages: 'Saved. &lt;n&gt; of &lt;total&gt; &lt;item&gt; units are out of service. No reservations were affected.'; amber panel 'Saved - &lt;n&gt; reservation(s) flagged for review, coordinators notified' listing '&lt;event&gt;: &lt;reserved&gt; reserved, &lt;available&gt; available'; 'All &lt;item&gt; units are back in service.'; too many: SPM-48's existing 'Only &lt;total&gt; units in total - cannot mark &lt;n&gt; as out of service'.</t>
         </is>
       </c>
-      <c r="C3" s="18" t="n"/>
+      <c r="C3" s="23" t="n"/>
     </row>
     <row r="4" ht="44.25" customHeight="1" s="19">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>DECIDED 2026-10-11: Technical Support's equipment request screen says 'out of service' instead of 'in maintenance' in its availability line, since units may also be damaged or unavailable (TC02, TC03).</t>
         </is>
       </c>
-      <c r="C4" s="18" t="n"/>
+      <c r="C4" s="23" t="n"/>
     </row>
     <row r="5" ht="165.75" customHeight="1" s="19">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>DECIDED 2026-10-11: Fixtures (scripts/seed-spm55.ts, npm run fixtures:spm55) - dedicated items so no other story's equipment changes: 'SPM55 Laser Projector' (4, none out), 'SPM55 Wireless Presenter' (6; Reserved 4 for 'SPM55 Harbour Product Launch' 10 Aug 2027 and 2 for 'SPM55 Quiet Board Meeting' 24 Aug 2027, 6 for completed 'SPM55 Past Roadshow' 1 Sep 2026), 'SPM55 Stage Monitor' (6; 3 each for 'SPM55 Morning Showcase' and 'SPM55 Evening Showcase', 17 Aug 2027), 'SPM55 Spare Microphone Kit' (5, 3 out 'Under maintenance - Cable fault'); events 'SPM55 Availability Check Forum' (9 Aug 2027) and 'SPM55 Return Check Seminar' (23 Aug 2027) each requesting 4 SPM55 Laser Projectors, not reserved. All events in Planning (except the completed one), coordinator Daniel Tan.</t>
         </is>
       </c>
-      <c r="C5" s="18" t="n"/>
+      <c r="C5" s="23" t="n"/>
     </row>
     <row r="6" ht="71.25" customHeight="1" s="19">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>DECIDED 2026-10-11: AC6's 'authorised users' are the new permission equipment:view_status (Coordinator, Operations Manager, Technical Support). The organiser keeps equipment:view for the request form, but GET /api/equipment no longer sends them the out-of-service count, type or reason.</t>
         </is>
       </c>
-      <c r="C6" s="18" t="n"/>
+      <c r="C6" s="23" t="n"/>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="19"/>
     <row r="22" ht="15.75" customHeight="1" s="19"/>
@@ -8219,7 +8239,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-55-TC01</t>
         </is>
@@ -8231,7 +8251,7 @@
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Technical Support record some units of an item as under maintenance, with a reason</t>
         </is>
@@ -8243,7 +8263,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>npm run fixtures:spm55 has been run. 'SPM55 Laser Projector' has 4 units in total and none out of service. Logged in as Technical Support Kenji Sato (kenji.sato@connectsphere.com / password123). This case changes the item - SPM-55-TC02 and TC03 read the result, so go straight to those and run npm run fixtures:spm55 after TC03.</t>
         </is>
@@ -8255,7 +8275,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>1. Click 'Equipment' in the sidebar
 2. Click 'Record unavailability' on the 'SPM55 Laser Projector' row
@@ -8272,7 +8292,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Item: SPM55 Laser Projector (4 units)
 Units out of service: 2
@@ -8287,7 +8307,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Step 1: The Equipment page lists the catalogue. 'SPM55 Laser Projector' shows Total units 4, Out of service 0 and the status 'Available'.
 Step 2: A dialog headed 'Record unavailability - SPM55 Laser Projector' opens with 'Units out of service', 'Type' and 'Reason (optional)'.
@@ -8301,7 +8321,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -8333,7 +8353,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>Step 1: The Equipment page lists the catalogue. 'SPM55 Laser Projector' shows Total units 4, Out of service 0 and the status 'Available'.
 Step 2: A dialog headed 'Record unavailability - SPM55 Laser Projector' opens with 'Units out of service', 'Type' and 'Reason (optional)'.
@@ -8402,7 +8422,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>Step 1: The Equipment page lists the catalogue. 'SPM55 Laser Projector' shows Total units 4, Out of service 0 and the status 'Available'.
 Step 2: A dialog headed 'Record unavailability - SPM55 Laser Projector' opens with 'Units out of service', 'Type' and 'Reason (optional)'.
@@ -9467,7 +9487,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-55-TC02</t>
         </is>
@@ -9479,7 +9499,7 @@
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Units out of service are left out of the availability check and of what Reserve takes</t>
         </is>
@@ -9491,7 +9511,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>SPM-55-TC01 has just been run (so 2 of the 4 'SPM55 Laser Projector' units are out of service) and the fixtures have NOT been reset since. 'SPM55 Availability Check Forum' (Planning, 9 Aug 2027) requests 4 SPM55 Laser Projectors, not yet reserved, and nothing else holds them that week. Still logged in as Kenji Sato.</t>
         </is>
@@ -9503,7 +9523,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>1. Click 'Equipment Requests' in the sidebar
 2. Click 'SPM55 Availability Check Forum' in the list
@@ -9517,7 +9537,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Event: SPM55 Availability Check Forum (Planning)
 Request: SPM55 Laser Projector x 4
@@ -9531,7 +9551,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Step 2: The 'SPM55 Laser Projector' line reads '4 total − 2 out of service − 0 reserved elsewhere = 2 available for these dates' and '4 requested, 2 available.', with the availability chip 'Partial'.
 Step 3: The message 'Reservation saved: 2 reserved.' is shown and the line's status becomes 'Partially fulfilled' with 2 reserved - the 2 units out of service were not reserved.</t>
@@ -9544,7 +9564,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -9576,7 +9596,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>Step 2: The 'SPM55 Laser Projector' line reads '4 total − 2 out of service − 0 reserved elsewhere = 2 available for these dates' and '4 requested, 2 available.', with the availability chip 'Partial'.
 Step 3: The message 'Reservation saved: 2 reserved.' is shown and the line's status becomes 'Partially fulfilled' with 2 reserved - the 2 units out of service were not reserved.</t>
@@ -9644,7 +9664,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>Step 2: The 'SPM55 Laser Projector' line reads '4 total − 2 out of service − 0 reserved elsewhere = 2 available for these dates' and '4 requested, 2 available.', with the availability chip 'Partial'.
 Step 3: The message 'Reservation saved: 2 reserved.' is shown and the line's status becomes 'Partially fulfilled' with 2 reserved - the 2 units out of service were not reserved.</t>
@@ -10708,7 +10728,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-55-TC03</t>
         </is>
@@ -10720,7 +10740,7 @@
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Returning every unit to available counts them in the availability check again</t>
         </is>
@@ -10732,7 +10752,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>SPM-55-TC02 has just been run (2 of the 4 'SPM55 Laser Projector' units out of service, 2 reserved for SPM55 Availability Check Forum) and the fixtures have NOT been reset since. 'SPM55 Return Check Seminar' (Planning, 23 Aug 2027) requests 4 SPM55 Laser Projectors, not yet reserved; nothing else holds them that week. Still logged in as Kenji Sato. Run npm run fixtures:spm55 after this case.</t>
         </is>
@@ -10744,7 +10764,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>1. Click 'Equipment' in the sidebar
 2. Click 'Return all to available' on the 'SPM55 Laser Projector' row
@@ -10760,7 +10780,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Item: SPM55 Laser Projector (2 of 4 out of service)
 Event: SPM55 Return Check Seminar (Planning), requests 4</t>
@@ -10773,7 +10793,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Step 2: A dialog headed 'Return all units to available?' says the 2 units out of service will be counted as available again.
 Step 3: The message 'All SPM55 Laser Projector units are back in service.' is shown. The row shows Out of service 0, the status 'Available', and the Reason column shows '—'.
@@ -10787,7 +10807,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -10819,7 +10839,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>Step 2: A dialog headed 'Return all units to available?' says the 2 units out of service will be counted as available again.
 Step 3: The message 'All SPM55 Laser Projector units are back in service.' is shown. The row shows Out of service 0, the status 'Available', and the Reason column shows '—'.
@@ -10857,7 +10877,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -10888,7 +10908,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>Step 2: A dialog headed 'Return all units to available?' says the 2 units out of service will be counted as available again.
 Step 3: The message 'All SPM55 Laser Projector units are back in service.' is shown. The row shows Out of service 0, the status 'Available', and the Reason column shows '—'.
@@ -11953,7 +11973,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-55-TC04</t>
         </is>
@@ -11965,7 +11985,7 @@
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Every unit of an item can be marked damaged, without a reason</t>
         </is>
@@ -11977,7 +11997,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>npm run fixtures:spm55 has been run. 'SPM55 Laser Projector' has 4 units in total, none out of service, and no reservations. Logged in as Kenji Sato (kenji.sato@connectsphere.com / password123). This case changes the item - run npm run fixtures:spm55 afterwards.</t>
         </is>
@@ -11989,7 +12009,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>1. Click 'Equipment' in the sidebar
 2. Click 'Record unavailability' on the 'SPM55 Laser Projector' row
@@ -12006,7 +12026,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Item: SPM55 Laser Projector (4 units)
 Units out of service: 4 (all)
@@ -12021,7 +12041,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Step 6: The message 'Saved. 4 of 4 SPM55 Laser Projector units are out of service. No reservations were affected.' is shown. The row shows Out of service 4, the status 'Out of service', and 'Damaged' alone in the Reason column - a reason is optional.</t>
         </is>
@@ -12033,7 +12053,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -12065,7 +12085,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>Step 6: The message 'Saved. 4 of 4 SPM55 Laser Projector units are out of service. No reservations were affected.' is shown. The row shows Out of service 4, the status 'Out of service', and 'Damaged' alone in the Reason column - a reason is optional.</t>
         </is>
@@ -12132,7 +12152,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>Step 6: The message 'Saved. 4 of 4 SPM55 Laser Projector units are out of service. No reservations were affected.' is shown. The row shows Out of service 4, the status 'Out of service', and 'Damaged' alone in the Reason column - a reason is optional.</t>
         </is>
@@ -13195,7 +13215,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-55-TC05</t>
         </is>
@@ -13207,7 +13227,7 @@
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>More units than the item has cannot be marked out of service</t>
         </is>
@@ -13219,7 +13239,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>npm run fixtures:spm55 has been run. 'SPM55 Laser Projector' has 4 units in total, none out of service. Logged in as Kenji Sato (kenji.sato@connectsphere.com / password123).</t>
         </is>
@@ -13231,7 +13251,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>1. Click 'Equipment' in the sidebar
 2. Click 'Record unavailability' on the 'SPM55 Laser Projector' row
@@ -13248,7 +13268,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Item: SPM55 Laser Projector (4 units)
 Units out of service: 5</t>
@@ -13261,7 +13281,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Step 5: Nothing is saved. The message 'Only 4 units in total - cannot mark 5 as out of service' is shown under 'Units out of service' and the dialog stays open.
 Step 6: The row still shows Out of service 0 and the status 'Available'.</t>
@@ -13274,7 +13294,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -13306,7 +13326,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>Step 5: Nothing is saved. The message 'Only 4 units in total - cannot mark 5 as out of service' is shown under 'Units out of service' and the dialog stays open.
 Step 6: The row still shows Out of service 0 and the status 'Available'.</t>
@@ -13343,7 +13363,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -13374,7 +13394,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>Step 5: Nothing is saved. The message 'Only 4 units in total - cannot mark 5 as out of service' is shown under 'Units out of service' and the dialog stays open.
 Step 6: The row still shows Out of service 0 and the status 'Available'.</t>
@@ -14438,7 +14458,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-55-TC06</t>
         </is>
@@ -14450,7 +14470,7 @@
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>A reservation left short is flagged for review, not cancelled, and its Coordinator notified</t>
         </is>
@@ -14462,7 +14482,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>npm run fixtures:spm55 has been run. 'SPM55 Wireless Presenter' has 6 units, none out of service. It is Reserved: 4 for 'SPM55 Harbour Product Launch' (Planning, 10 Aug 2027, coordinator Daniel Tan), 2 for 'SPM55 Quiet Board Meeting' (Planning, 24 Aug 2027) and 6 for 'SPM55 Past Roadshow' (Completed, 1 Sep 2026). Logged in as Kenji Sato (kenji.sato@connectsphere.com / password123). This case changes the item - run npm run fixtures:spm55 afterwards.</t>
         </is>
@@ -14474,7 +14494,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>1. Click 'Equipment' in the sidebar
 2. Click 'Record unavailability' on the 'SPM55 Wireless Presenter' row
@@ -14496,7 +14516,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Item: SPM55 Wireless Presenter (6 units), 3 marked Damaged
 Reservations: Harbour Product Launch 4 (upcoming), Quiet Board Meeting 2 (upcoming), Past Roadshow 6 (completed)</t>
@@ -14509,7 +14529,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Step 6: An amber panel reads 'Saved - 1 reservation flagged for review, coordinators notified'. It lists 'SPM55 Harbour Product Launch: 4 reserved, 3 available' and says the reservation has NOT been changed or cancelled. 'SPM55 Quiet Board Meeting' (2 reserved, 3 still enough) and 'SPM55 Past Roadshow' (already over) are not listed.
 Step 11: The 'SPM55 Wireless Presenter' requirement is still listed with status 'Reserved' and 4 reserved - flagging did not cancel or reduce it.</t>
@@ -14522,7 +14542,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -14554,7 +14574,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>Step 6: An amber panel reads 'Saved - 1 reservation flagged for review, coordinators notified'. It lists 'SPM55 Harbour Product Launch: 4 reserved, 3 available' and says the reservation has NOT been changed or cancelled. 'SPM55 Quiet Board Meeting' (2 reserved, 3 still enough) and 'SPM55 Past Roadshow' (already over) are not listed.
 Step 11: The 'SPM55 Wireless Presenter' requirement is still listed with status 'Reserved' and 4 reserved - flagging did not cancel or reduce it.</t>
@@ -14591,7 +14611,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -14622,7 +14642,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>Step 6: An amber panel reads 'Saved - 1 reservation flagged for review, coordinators notified'. It lists 'SPM55 Harbour Product Launch: 4 reserved, 3 available' and says the reservation has NOT been changed or cancelled. 'SPM55 Quiet Board Meeting' (2 reserved, 3 still enough) and 'SPM55 Past Roadshow' (already over) are not listed.
 Step 11: The 'SPM55 Wireless Presenter' requirement is still listed with status 'Reserved' and 4 reserved - flagging did not cancel or reduce it.</t>
@@ -15686,7 +15706,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-55-TC07</t>
         </is>
@@ -15698,7 +15718,7 @@
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>A reservation that is exactly covered by the units left is not flagged</t>
         </is>
@@ -15710,7 +15730,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>npm run fixtures:spm55 has been run (the same reservations as SPM-55-TC06: 'SPM55 Wireless Presenter' has 6 units, 4 reserved for 'SPM55 Harbour Product Launch'). Logged in as Kenji Sato (kenji.sato@connectsphere.com / password123). This case changes the item - run npm run fixtures:spm55 afterwards.</t>
         </is>
@@ -15722,7 +15742,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>1. Click 'Equipment' in the sidebar
 2. Click 'Record unavailability' on the 'SPM55 Wireless Presenter' row
@@ -15738,7 +15758,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Item: SPM55 Wireless Presenter (6 units), 2 out of service - leaves 4, exactly the 4 reserved</t>
         </is>
@@ -15750,7 +15770,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Step 5: The message 'Saved. 2 of 6 SPM55 Wireless Presenter units are out of service. No reservations were affected.' is shown - the 4 units left still cover the 4 reserved, so nothing is flagged and no one is notified.</t>
         </is>
@@ -15762,7 +15782,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -15794,7 +15814,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>Step 5: The message 'Saved. 2 of 6 SPM55 Wireless Presenter units are out of service. No reservations were affected.' is shown - the 4 units left still cover the 4 reserved, so nothing is flagged and no one is notified.</t>
         </is>
@@ -15830,7 +15850,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -15861,7 +15881,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>Step 5: The message 'Saved. 2 of 6 SPM55 Wireless Presenter units are out of service. No reservations were affected.' is shown - the 4 units left still cover the 4 reserved, so nothing is flagged and no one is notified.</t>
         </is>
